--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Llama-3.3-70B-Instruct/metrics_default_vs_simple.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Llama-3.3-70B-Instruct/metrics_default_vs_simple.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.3292682926829268</v>
+        <v>0.3103448275862069</v>
       </c>
       <c r="B2">
-        <v>0.03125</v>
+        <v>0.03225806451612903</v>
       </c>
       <c r="C2">
-        <v>0.3943661971830986</v>
+        <v>0.3661971830985916</v>
       </c>
       <c r="D2">
-        <v>0.7543859649122807</v>
+        <v>0.7627118644067796</v>
       </c>
       <c r="E2">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G2">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
